--- a/public/export.xlsx
+++ b/public/export.xlsx
@@ -552,6 +552,27 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -563,47 +584,12 @@
     </xf>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="41">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="39">
     <dxf>
       <fill>
         <patternFill>
@@ -1758,44 +1744,44 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9ECC7F61-537F-4A22-A5D3-2D61D40ED19D}" name="Table1" displayName="Table1" ref="A7:AF8" totalsRowShown="0" headerRowDxfId="40" dataDxfId="38" headerRowBorderDxfId="39" tableBorderDxfId="37" totalsRowBorderDxfId="36">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9ECC7F61-537F-4A22-A5D3-2D61D40ED19D}" name="Table1" displayName="Table1" ref="A7:AF8" totalsRowShown="0" headerRowDxfId="38" dataDxfId="36" headerRowBorderDxfId="37" tableBorderDxfId="35" totalsRowBorderDxfId="34">
   <autoFilter ref="A7:AF8" xr:uid="{7BFAA509-C733-475B-A74D-F30DBBD3F86D}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A8:AF8">
     <sortCondition ref="G8"/>
   </sortState>
   <tableColumns count="32">
-    <tableColumn id="1" xr3:uid="{2D5E0CC1-421C-4776-AFE1-531CADA5E6EA}" name="1" dataDxfId="35"/>
-    <tableColumn id="2" xr3:uid="{F89ADE37-12F0-492D-8C28-57607FD9BF35}" name="edrpou" dataDxfId="34"/>
-    <tableColumn id="3" xr3:uid="{A2E4B3E9-3FD8-45DB-9F00-1D2CC1E9ACA2}" name="edrpou_check" dataDxfId="33"/>
-    <tableColumn id="5" xr3:uid="{8DD2CD67-2B6E-4D14-99F5-83F46B759260}" name="2" dataDxfId="32"/>
-    <tableColumn id="6" xr3:uid="{9BC8EA17-125A-49AF-BB24-3CCE6AB3E990}" name="3" dataDxfId="31"/>
-    <tableColumn id="7" xr3:uid="{82956D0A-42F7-4956-B8DE-ED4235134CA9}" name="4" dataDxfId="30"/>
-    <tableColumn id="8" xr3:uid="{55C3E3B8-9C13-4271-BF25-F62A6EC463D4}" name="5" dataDxfId="29"/>
-    <tableColumn id="9" xr3:uid="{461AB30D-0158-4CB4-9AEF-6592FA3AAB16}" name="6" dataDxfId="28"/>
-    <tableColumn id="10" xr3:uid="{8E1449FD-783D-4875-8C0B-71B362B3B5B1}" name="7" dataDxfId="27"/>
-    <tableColumn id="11" xr3:uid="{3BEEE9F3-3D63-4D19-BA5D-50EAB3341FBD}" name="8" dataDxfId="26"/>
-    <tableColumn id="12" xr3:uid="{68DB51E6-C4A7-4A73-B0F2-598F59827269}" name="9" dataDxfId="25"/>
-    <tableColumn id="13" xr3:uid="{06BDD904-0C05-4EB4-9AB6-05833713D55F}" name="10" dataDxfId="24"/>
-    <tableColumn id="14" xr3:uid="{CEE9FE7E-88F7-482B-82BB-CF41CC469047}" name="11" dataDxfId="23"/>
-    <tableColumn id="15" xr3:uid="{253EACB6-CAAE-48A7-AAFC-AB9EE7898759}" name="12" dataDxfId="22"/>
-    <tableColumn id="16" xr3:uid="{4A59C18E-3AC0-4770-987E-930115D73356}" name="13" dataDxfId="21"/>
-    <tableColumn id="17" xr3:uid="{1090A053-C6E3-4D08-B841-3DE9CF8DBD35}" name="14" dataDxfId="20"/>
-    <tableColumn id="18" xr3:uid="{8670A9CA-FBB9-4CC2-8ABB-3DF7C8F4EF5F}" name="15" dataDxfId="19"/>
-    <tableColumn id="19" xr3:uid="{08B36A9B-91A3-4F0D-AAE6-8F5BF0458A9F}" name="16" dataDxfId="18"/>
-    <tableColumn id="20" xr3:uid="{F2FFD126-9046-4CF9-97AF-6EE9FB387C6A}" name="17" dataDxfId="17"/>
-    <tableColumn id="21" xr3:uid="{7A641FA7-D98A-455F-B05F-264C455F7860}" name="18" dataDxfId="16"/>
-    <tableColumn id="22" xr3:uid="{E3E56FDE-7D48-4E31-A0FE-6A8E0455E103}" name="19" dataDxfId="15"/>
-    <tableColumn id="23" xr3:uid="{3ADB2F1F-B1F4-40B6-B403-EC64E29F486F}" name="20" dataDxfId="14"/>
-    <tableColumn id="24" xr3:uid="{CEC4C9F0-87FA-4E5A-A51E-5A4AD953E19B}" name="21" dataDxfId="13"/>
-    <tableColumn id="25" xr3:uid="{E4B315BE-B047-4D13-9340-2BACA849E671}" name="22" dataDxfId="12"/>
-    <tableColumn id="26" xr3:uid="{2CA6615F-1E74-4287-B42C-A8E7B15A30FA}" name="23" dataDxfId="11"/>
-    <tableColumn id="27" xr3:uid="{57F5A50D-2B89-4279-8CDD-B1B776CA8223}" name="24" dataDxfId="10"/>
-    <tableColumn id="28" xr3:uid="{4635D351-2EEE-4853-ABA0-79E5A603ED12}" name="25" dataDxfId="9"/>
-    <tableColumn id="29" xr3:uid="{473AC97E-2947-4A40-A7AF-2CAA8DBA9DB8}" name="26" dataDxfId="8"/>
-    <tableColumn id="30" xr3:uid="{D39AD032-6D67-4DB4-8E65-6E16AF31178B}" name="27" dataDxfId="7"/>
-    <tableColumn id="31" xr3:uid="{080F6361-4F04-4FF5-A48B-90F8BD4AF3E1}" name="28" dataDxfId="6"/>
-    <tableColumn id="32" xr3:uid="{2554CA2D-CF40-4435-A14C-57377ACB7246}" name="29" dataDxfId="5"/>
-    <tableColumn id="33" xr3:uid="{060FE0BA-FEC8-4352-91A9-6D2A435F03E8}" name="30" dataDxfId="4"/>
+    <tableColumn id="1" xr3:uid="{2D5E0CC1-421C-4776-AFE1-531CADA5E6EA}" name="1" dataDxfId="33"/>
+    <tableColumn id="2" xr3:uid="{F89ADE37-12F0-492D-8C28-57607FD9BF35}" name="edrpou" dataDxfId="32"/>
+    <tableColumn id="3" xr3:uid="{A2E4B3E9-3FD8-45DB-9F00-1D2CC1E9ACA2}" name="edrpou_check" dataDxfId="31"/>
+    <tableColumn id="5" xr3:uid="{8DD2CD67-2B6E-4D14-99F5-83F46B759260}" name="2" dataDxfId="30"/>
+    <tableColumn id="6" xr3:uid="{9BC8EA17-125A-49AF-BB24-3CCE6AB3E990}" name="3" dataDxfId="29"/>
+    <tableColumn id="7" xr3:uid="{82956D0A-42F7-4956-B8DE-ED4235134CA9}" name="4" dataDxfId="28"/>
+    <tableColumn id="8" xr3:uid="{55C3E3B8-9C13-4271-BF25-F62A6EC463D4}" name="5" dataDxfId="27"/>
+    <tableColumn id="9" xr3:uid="{461AB30D-0158-4CB4-9AEF-6592FA3AAB16}" name="6" dataDxfId="26"/>
+    <tableColumn id="10" xr3:uid="{8E1449FD-783D-4875-8C0B-71B362B3B5B1}" name="7" dataDxfId="25"/>
+    <tableColumn id="11" xr3:uid="{3BEEE9F3-3D63-4D19-BA5D-50EAB3341FBD}" name="8" dataDxfId="24"/>
+    <tableColumn id="12" xr3:uid="{68DB51E6-C4A7-4A73-B0F2-598F59827269}" name="9" dataDxfId="23"/>
+    <tableColumn id="13" xr3:uid="{06BDD904-0C05-4EB4-9AB6-05833713D55F}" name="10" dataDxfId="22"/>
+    <tableColumn id="14" xr3:uid="{CEE9FE7E-88F7-482B-82BB-CF41CC469047}" name="11" dataDxfId="21"/>
+    <tableColumn id="15" xr3:uid="{253EACB6-CAAE-48A7-AAFC-AB9EE7898759}" name="12" dataDxfId="20"/>
+    <tableColumn id="16" xr3:uid="{4A59C18E-3AC0-4770-987E-930115D73356}" name="13" dataDxfId="19"/>
+    <tableColumn id="17" xr3:uid="{1090A053-C6E3-4D08-B841-3DE9CF8DBD35}" name="14" dataDxfId="18"/>
+    <tableColumn id="18" xr3:uid="{8670A9CA-FBB9-4CC2-8ABB-3DF7C8F4EF5F}" name="15" dataDxfId="17"/>
+    <tableColumn id="19" xr3:uid="{08B36A9B-91A3-4F0D-AAE6-8F5BF0458A9F}" name="16" dataDxfId="16"/>
+    <tableColumn id="20" xr3:uid="{F2FFD126-9046-4CF9-97AF-6EE9FB387C6A}" name="17" dataDxfId="15"/>
+    <tableColumn id="21" xr3:uid="{7A641FA7-D98A-455F-B05F-264C455F7860}" name="18" dataDxfId="14"/>
+    <tableColumn id="22" xr3:uid="{E3E56FDE-7D48-4E31-A0FE-6A8E0455E103}" name="19" dataDxfId="13"/>
+    <tableColumn id="23" xr3:uid="{3ADB2F1F-B1F4-40B6-B403-EC64E29F486F}" name="20" dataDxfId="12"/>
+    <tableColumn id="24" xr3:uid="{CEC4C9F0-87FA-4E5A-A51E-5A4AD953E19B}" name="21" dataDxfId="11"/>
+    <tableColumn id="25" xr3:uid="{E4B315BE-B047-4D13-9340-2BACA849E671}" name="22" dataDxfId="10"/>
+    <tableColumn id="26" xr3:uid="{2CA6615F-1E74-4287-B42C-A8E7B15A30FA}" name="23" dataDxfId="9"/>
+    <tableColumn id="27" xr3:uid="{57F5A50D-2B89-4279-8CDD-B1B776CA8223}" name="24" dataDxfId="8"/>
+    <tableColumn id="28" xr3:uid="{4635D351-2EEE-4853-ABA0-79E5A603ED12}" name="25" dataDxfId="7"/>
+    <tableColumn id="29" xr3:uid="{473AC97E-2947-4A40-A7AF-2CAA8DBA9DB8}" name="26" dataDxfId="6"/>
+    <tableColumn id="30" xr3:uid="{D39AD032-6D67-4DB4-8E65-6E16AF31178B}" name="27" dataDxfId="5"/>
+    <tableColumn id="31" xr3:uid="{080F6361-4F04-4FF5-A48B-90F8BD4AF3E1}" name="28" dataDxfId="4"/>
+    <tableColumn id="32" xr3:uid="{2554CA2D-CF40-4435-A14C-57377ACB7246}" name="29" dataDxfId="3"/>
+    <tableColumn id="33" xr3:uid="{060FE0BA-FEC8-4352-91A9-6D2A435F03E8}" name="30" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2159,13 +2145,13 @@
       <c r="X1" s="8"/>
       <c r="Y1" s="4"/>
       <c r="Z1" s="2"/>
-      <c r="AA1" s="28" t="s">
+      <c r="AA1" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="AB1" s="28"/>
-      <c r="AC1" s="28"/>
-      <c r="AD1" s="28"/>
-      <c r="AE1" s="28"/>
+      <c r="AB1" s="35"/>
+      <c r="AC1" s="35"/>
+      <c r="AD1" s="35"/>
+      <c r="AE1" s="35"/>
       <c r="AF1" s="9"/>
     </row>
     <row r="2" spans="1:33" x14ac:dyDescent="0.55000000000000004">
@@ -2203,39 +2189,39 @@
       <c r="AF2" s="9"/>
     </row>
     <row r="3" spans="1:33" ht="46.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="29" t="s">
+      <c r="A3" s="36" t="s">
         <v>95</v>
       </c>
-      <c r="B3" s="30"/>
-      <c r="C3" s="30"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="30"/>
-      <c r="H3" s="30"/>
-      <c r="I3" s="30"/>
-      <c r="J3" s="30"/>
-      <c r="K3" s="31"/>
-      <c r="L3" s="30"/>
-      <c r="M3" s="30"/>
-      <c r="N3" s="30"/>
-      <c r="O3" s="30"/>
-      <c r="P3" s="30"/>
-      <c r="Q3" s="30"/>
-      <c r="R3" s="30"/>
-      <c r="S3" s="30"/>
-      <c r="T3" s="30"/>
-      <c r="U3" s="30"/>
-      <c r="V3" s="30"/>
-      <c r="W3" s="30"/>
-      <c r="X3" s="30"/>
-      <c r="Y3" s="30"/>
-      <c r="Z3" s="30"/>
-      <c r="AA3" s="30"/>
-      <c r="AB3" s="30"/>
-      <c r="AC3" s="30"/>
-      <c r="AD3" s="30"/>
-      <c r="AE3" s="30"/>
+      <c r="B3" s="37"/>
+      <c r="C3" s="37"/>
+      <c r="D3" s="37"/>
+      <c r="E3" s="37"/>
+      <c r="F3" s="37"/>
+      <c r="G3" s="37"/>
+      <c r="H3" s="37"/>
+      <c r="I3" s="37"/>
+      <c r="J3" s="37"/>
+      <c r="K3" s="38"/>
+      <c r="L3" s="37"/>
+      <c r="M3" s="37"/>
+      <c r="N3" s="37"/>
+      <c r="O3" s="37"/>
+      <c r="P3" s="37"/>
+      <c r="Q3" s="37"/>
+      <c r="R3" s="37"/>
+      <c r="S3" s="37"/>
+      <c r="T3" s="37"/>
+      <c r="U3" s="37"/>
+      <c r="V3" s="37"/>
+      <c r="W3" s="37"/>
+      <c r="X3" s="37"/>
+      <c r="Y3" s="37"/>
+      <c r="Z3" s="37"/>
+      <c r="AA3" s="37"/>
+      <c r="AB3" s="37"/>
+      <c r="AC3" s="37"/>
+      <c r="AD3" s="37"/>
+      <c r="AE3" s="37"/>
       <c r="AF3" s="9"/>
     </row>
     <row r="4" spans="1:33" x14ac:dyDescent="0.55000000000000004">
@@ -2273,152 +2259,152 @@
       <c r="AF4" s="9"/>
     </row>
     <row r="5" spans="1:33" ht="140.1" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="35" t="s">
+      <c r="A5" s="30" t="s">
         <v>84</v>
       </c>
-      <c r="B5" s="33" t="s">
+      <c r="B5" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="33" t="s">
+      <c r="C5" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="35" t="s">
+      <c r="D5" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="E5" s="35" t="s">
+      <c r="E5" s="30" t="s">
         <v>85</v>
       </c>
-      <c r="F5" s="35"/>
-      <c r="G5" s="35" t="s">
+      <c r="F5" s="30"/>
+      <c r="G5" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="H5" s="35" t="s">
+      <c r="H5" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="I5" s="35" t="s">
+      <c r="I5" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="J5" s="35" t="s">
+      <c r="J5" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="K5" s="36" t="s">
+      <c r="K5" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="L5" s="35" t="s">
+      <c r="L5" s="30" t="s">
         <v>86</v>
       </c>
-      <c r="M5" s="35"/>
-      <c r="N5" s="35"/>
-      <c r="O5" s="35"/>
-      <c r="P5" s="35"/>
-      <c r="Q5" s="35" t="s">
+      <c r="M5" s="30"/>
+      <c r="N5" s="30"/>
+      <c r="O5" s="30"/>
+      <c r="P5" s="30"/>
+      <c r="Q5" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="R5" s="35"/>
-      <c r="S5" s="35"/>
-      <c r="T5" s="35"/>
-      <c r="U5" s="35"/>
-      <c r="V5" s="35" t="s">
+      <c r="R5" s="30"/>
+      <c r="S5" s="30"/>
+      <c r="T5" s="30"/>
+      <c r="U5" s="30"/>
+      <c r="V5" s="30" t="s">
         <v>81</v>
       </c>
-      <c r="W5" s="35" t="s">
+      <c r="W5" s="30" t="s">
         <v>82</v>
       </c>
-      <c r="X5" s="35"/>
-      <c r="Y5" s="35" t="s">
+      <c r="X5" s="30"/>
+      <c r="Y5" s="30" t="s">
         <v>83</v>
       </c>
-      <c r="Z5" s="35"/>
-      <c r="AA5" s="35" t="s">
+      <c r="Z5" s="30"/>
+      <c r="AA5" s="30" t="s">
         <v>89</v>
       </c>
-      <c r="AB5" s="35" t="s">
+      <c r="AB5" s="30" t="s">
         <v>90</v>
       </c>
-      <c r="AC5" s="37" t="s">
+      <c r="AC5" s="32" t="s">
         <v>91</v>
       </c>
-      <c r="AD5" s="37" t="s">
+      <c r="AD5" s="32" t="s">
         <v>94</v>
       </c>
-      <c r="AE5" s="37"/>
-      <c r="AF5" s="37"/>
-      <c r="AG5" s="32" t="s">
+      <c r="AE5" s="32"/>
+      <c r="AF5" s="32"/>
+      <c r="AG5" s="34" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:33" ht="43.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="38"/>
-      <c r="B6" s="34"/>
-      <c r="C6" s="34"/>
-      <c r="D6" s="35"/>
-      <c r="E6" s="35" t="s">
+      <c r="A6" s="33"/>
+      <c r="B6" s="29"/>
+      <c r="C6" s="29"/>
+      <c r="D6" s="30"/>
+      <c r="E6" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="37" t="s">
+      <c r="F6" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="G6" s="35"/>
-      <c r="H6" s="35"/>
-      <c r="I6" s="35"/>
-      <c r="J6" s="35"/>
-      <c r="K6" s="36"/>
-      <c r="L6" s="35" t="s">
+      <c r="G6" s="30"/>
+      <c r="H6" s="30"/>
+      <c r="I6" s="30"/>
+      <c r="J6" s="30"/>
+      <c r="K6" s="31"/>
+      <c r="L6" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="M6" s="35" t="s">
+      <c r="M6" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="N6" s="35" t="s">
+      <c r="N6" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="O6" s="35" t="s">
+      <c r="O6" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="P6" s="35" t="s">
+      <c r="P6" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="Q6" s="35" t="s">
+      <c r="Q6" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="R6" s="35" t="s">
+      <c r="R6" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="S6" s="35" t="s">
+      <c r="S6" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="T6" s="35" t="s">
+      <c r="T6" s="30" t="s">
         <v>88</v>
       </c>
-      <c r="U6" s="35" t="s">
+      <c r="U6" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="V6" s="35"/>
-      <c r="W6" s="35" t="s">
+      <c r="V6" s="30"/>
+      <c r="W6" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="X6" s="35" t="s">
+      <c r="X6" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="Y6" s="35" t="s">
+      <c r="Y6" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="Z6" s="35" t="s">
+      <c r="Z6" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="AA6" s="35"/>
-      <c r="AB6" s="35"/>
-      <c r="AC6" s="37"/>
-      <c r="AD6" s="37" t="s">
+      <c r="AA6" s="30"/>
+      <c r="AB6" s="30"/>
+      <c r="AC6" s="32"/>
+      <c r="AD6" s="32" t="s">
         <v>92</v>
       </c>
-      <c r="AE6" s="37" t="s">
+      <c r="AE6" s="32" t="s">
         <v>93</v>
       </c>
-      <c r="AF6" s="37" t="s">
+      <c r="AF6" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="AG6" s="32"/>
+      <c r="AG6" s="34"/>
     </row>
     <row r="7" spans="1:33" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="11" t="s">
@@ -2517,7 +2503,7 @@
       <c r="AF7" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="AG7" s="32"/>
+      <c r="AG7" s="34"/>
     </row>
     <row r="8" spans="1:33" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="15" t="s">
